--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-ips-organization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-ips-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2930" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3182" uniqueCount="431">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T10:23:49+00:00</t>
+    <t>2025-01-15T11:57:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -498,6 +498,15 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>Organization.identifier:GDA-OID</t>
+  </si>
+  <si>
+    <t>GDA-OID</t>
+  </si>
+  <si>
+    <t>Organization.identifier:GDA-OID.id</t>
+  </si>
+  <si>
     <t>Organization.identifier.id</t>
   </si>
   <si>
@@ -517,6 +526,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>Organization.identifier:GDA-OID.extension</t>
+  </si>
+  <si>
     <t>Organization.identifier.extension</t>
   </si>
   <si>
@@ -533,6 +545,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>Organization.identifier:GDA-OID.use</t>
+  </si>
+  <si>
     <t>Organization.identifier.use</t>
   </si>
   <si>
@@ -561,6 +576,9 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Organization.identifier:GDA-OID.type</t>
   </si>
   <si>
     <t>Organization.identifier.type</t>
@@ -585,7 +603,10 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/hl7-at-patientidentifier</t>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -594,10 +615,13 @@
     <t>CX.5</t>
   </si>
   <si>
+    <t>Organization.identifier:GDA-OID.system</t>
+  </si>
+  <si>
     <t>Organization.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
+    <t>A GDA in Austria is represented via an URI (OID)</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -609,6 +633,9 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>urn:ietf:rfc:3986</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
@@ -624,10 +651,13 @@
     <t>./IdentifierType</t>
   </si>
   <si>
+    <t>Organization.identifier:GDA-OID.value</t>
+  </si>
+  <si>
     <t>Organization.identifier.value</t>
   </si>
   <si>
-    <t>The value that is unique</t>
+    <t>OID for the GDA in Austria</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
@@ -649,6 +679,9 @@
   </si>
   <si>
     <t>./Value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:GDA-OID.period</t>
   </si>
   <si>
     <t>Organization.identifier.period</t>
@@ -676,6 +709,9 @@
     <t>./StartDate and ./EndDate</t>
   </si>
   <si>
+    <t>Organization.identifier:GDA-OID.assigner</t>
+  </si>
+  <si>
     <t>Organization.identifier.assigner</t>
   </si>
   <si>
@@ -702,51 +738,6 @@
   </si>
   <si>
     <t>./IdentifierIssuingAuthority</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID</t>
-  </si>
-  <si>
-    <t>GDA-OID</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.type</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.system</t>
-  </si>
-  <si>
-    <t>A GDA in Austria is represented via an URI (OID)</t>
-  </si>
-  <si>
-    <t>urn:ietf:rfc:3986</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.value</t>
-  </si>
-  <si>
-    <t>OID for the GDA in Austria</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.period</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.assigner</t>
   </si>
   <si>
     <t>Organization.identifier:GDA-OID.assigner.id</t>
@@ -883,6 +874,9 @@
     <t>Organization.identifier:VPNR.value</t>
   </si>
   <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
     <t>Organization.identifier:VPNR.period</t>
   </si>
   <si>
@@ -965,6 +959,66 @@
   </si>
   <si>
     <t>Bundesministerium für Finanzen</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR</t>
+  </si>
+  <si>
+    <t>KANR</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.system</t>
+  </si>
+  <si>
+    <t>OID for the Krankenanstaltennummer (KA-Nr) in Austria</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.40.0.34.4.10</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.value</t>
+  </si>
+  <si>
+    <t>Krankenanstaltennummer according to Krankenanstaltenkataster. Virtual KANRs are suffixed with '+' (e.g. 'K101+')</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.assigner.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.assigner.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.assigner.reference</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.assigner.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.assigner.identifier</t>
+  </si>
+  <si>
+    <t>Organization.identifier:KANR.assigner.display</t>
+  </si>
+  <si>
+    <t>Österreichisches Bundesministerium für Gesundheit</t>
   </si>
   <si>
     <t>Organization.active</t>
@@ -1114,33 +1168,33 @@
 </t>
   </si>
   <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
-  </si>
-  <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
-  </si>
-  <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
+    <t>An address for the organization</t>
+  </si>
+  <si>
+    <t>An address for the organization.</t>
+  </si>
+  <si>
+    <t>Organization may have multiple addresses with different uses or applicable periods. The use code 'home' is not to be used.</t>
   </si>
   <si>
     <t>May need to keep track of the organization's addresses for contacting, billing or reporting requirements.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
+    <t xml:space="preserve">org-2
 </t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
-  </si>
-  <si>
-    <t>XAD</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>Address</t>
+org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
+  </si>
+  <si>
+    <t>ORC-23?</t>
+  </si>
+  <si>
+    <t>.address</t>
+  </si>
+  <si>
+    <t>./PrimaryAddress and ./OtherAddresses</t>
   </si>
   <si>
     <t>Organization.partOf</t>
@@ -1267,11 +1321,19 @@
     <t>Organization.contact.address</t>
   </si>
   <si>
+    <t>Visiting or postal addresses for the contact</t>
+  </si>
+  <si>
+    <t>Visiting or postal addresses for the contact.</t>
+  </si>
+  <si>
     <t>May need to keep track of a contact party's address for contacting, billing or reporting requirements.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
+    <t>PID-11</t>
+  </si>
+  <si>
+    <t>./addr</t>
   </si>
   <si>
     <t>Organization.endpoint</t>
@@ -1589,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN80"/>
+  <dimension ref="A1:AN87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.25390625" customWidth="true" bestFit="true"/>
@@ -2896,9 +2958,11 @@
         <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
       </c>
@@ -2916,19 +2980,21 @@
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
       </c>
@@ -2976,50 +3042,50 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>77</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -3031,17 +3097,15 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3078,37 +3142,37 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3119,46 +3183,44 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
@@ -3182,49 +3244,49 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3235,10 +3297,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3255,25 +3317,25 @@
         <v>77</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3298,11 +3360,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3320,7 +3384,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3335,10 +3399,10 @@
         <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3349,10 +3413,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3375,19 +3439,19 @@
         <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="O16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3400,43 +3464,43 @@
         <v>77</v>
       </c>
       <c r="T16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3451,13 +3515,13 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3465,10 +3529,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3476,7 +3540,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>86</v>
@@ -3491,24 +3555,26 @@
         <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="N17" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>77</v>
@@ -3582,7 +3648,7 @@
         <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3590,7 +3656,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>86</v>
@@ -3605,7 +3671,7 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>207</v>
@@ -3613,7 +3679,9 @@
       <c r="M18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N18" s="2"/>
+      <c r="N18" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3626,7 +3694,7 @@
         <v>77</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>77</v>
@@ -3662,7 +3730,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3677,13 +3745,13 @@
         <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3691,10 +3759,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3717,17 +3785,15 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3776,7 +3842,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3791,13 +3857,13 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3805,14 +3871,12 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3833,18 +3897,18 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>144</v>
+        <v>226</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3892,39 +3956,39 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>151</v>
+        <v>231</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>154</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3947,13 +4011,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4004,7 +4068,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4022,7 +4086,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -4033,10 +4097,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>161</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4065,7 +4129,7 @@
         <v>133</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>135</v>
@@ -4106,10 +4170,10 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
@@ -4118,7 +4182,7 @@
         <v>149</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4136,7 +4200,7 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4147,10 +4211,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>166</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4167,26 +4231,24 @@
         <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>167</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>168</v>
+        <v>241</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4210,13 +4272,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4234,7 +4296,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4243,16 +4305,16 @@
         <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4263,10 +4325,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>176</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4289,20 +4351,18 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>178</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
@@ -4326,13 +4386,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4350,7 +4410,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4365,10 +4425,10 @@
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4379,10 +4439,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4390,7 +4450,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>86</v>
@@ -4405,32 +4465,30 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>77</v>
@@ -4466,7 +4524,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>192</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4481,13 +4539,13 @@
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>194</v>
+        <v>259</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4495,10 +4553,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4506,7 +4564,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>86</v>
@@ -4521,16 +4579,16 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4538,13 +4596,13 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>77</v>
@@ -4580,7 +4638,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>201</v>
+        <v>266</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4595,13 +4653,13 @@
         <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>203</v>
+        <v>129</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4609,12 +4667,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4623,7 +4683,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4635,16 +4695,18 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>206</v>
+        <v>144</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>207</v>
+        <v>145</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4692,39 +4754,39 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>210</v>
+        <v>151</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>212</v>
+        <v>153</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>77</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>213</v>
+        <v>158</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4744,20 +4806,18 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4806,7 +4866,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4818,16 +4878,16 @@
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4835,21 +4895,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>238</v>
+        <v>165</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4861,15 +4921,17 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4906,37 +4968,37 @@
         <v>77</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4947,44 +5009,46 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>240</v>
+        <v>171</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5008,49 +5072,49 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>163</v>
+        <v>77</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5061,10 +5125,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>242</v>
+        <v>182</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5087,18 +5151,20 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5122,13 +5188,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5146,7 +5212,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5155,16 +5221,16 @@
         <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5175,10 +5241,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>249</v>
+        <v>194</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5186,7 +5252,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>86</v>
@@ -5204,27 +5270,29 @@
         <v>100</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>77</v>
+        <v>275</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>77</v>
@@ -5236,13 +5304,13 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>253</v>
+        <v>77</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>254</v>
+        <v>77</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -5260,7 +5328,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>255</v>
+        <v>201</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5275,13 +5343,13 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5289,10 +5357,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>257</v>
+        <v>206</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5300,7 +5368,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>86</v>
@@ -5315,16 +5383,16 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5338,7 +5406,7 @@
         <v>77</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>77</v>
@@ -5374,7 +5442,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>261</v>
+        <v>211</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5389,13 +5457,13 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>262</v>
+        <v>213</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5403,10 +5471,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5429,24 +5497,22 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>268</v>
+        <v>77</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>77</v>
@@ -5488,7 +5554,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5503,13 +5569,13 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>129</v>
+        <v>222</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5517,14 +5583,12 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5545,18 +5609,18 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>144</v>
+        <v>226</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5604,39 +5668,39 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>143</v>
+        <v>230</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>151</v>
+        <v>231</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>154</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5659,13 +5723,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5716,7 +5780,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5734,7 +5798,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5745,10 +5809,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>161</v>
+        <v>237</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5777,7 +5841,7 @@
         <v>133</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>135</v>
@@ -5818,10 +5882,10 @@
         <v>77</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>77</v>
@@ -5830,7 +5894,7 @@
         <v>149</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5848,7 +5912,7 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5859,10 +5923,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>166</v>
+        <v>239</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5879,26 +5943,24 @@
         <v>77</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>167</v>
+        <v>240</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>168</v>
+        <v>241</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -5922,13 +5984,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -5946,7 +6008,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5955,16 +6017,16 @@
         <v>86</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5975,10 +6037,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>176</v>
+        <v>246</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6001,20 +6063,18 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>178</v>
+        <v>247</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6038,13 +6098,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6062,7 +6122,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6077,10 +6137,10 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6091,10 +6151,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6102,7 +6162,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>86</v>
@@ -6117,32 +6177,30 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -6178,7 +6236,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>192</v>
+        <v>258</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6193,13 +6251,13 @@
         <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>194</v>
+        <v>259</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6207,10 +6265,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6218,7 +6276,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>86</v>
@@ -6233,16 +6291,16 @@
         <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6250,13 +6308,13 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>77</v>
@@ -6292,7 +6350,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>201</v>
+        <v>266</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6307,13 +6365,13 @@
         <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>203</v>
+        <v>129</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6321,12 +6379,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6347,16 +6407,18 @@
         <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>206</v>
+        <v>144</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>207</v>
+        <v>145</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6404,39 +6466,39 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>210</v>
+        <v>151</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>212</v>
+        <v>153</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>77</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>213</v>
+        <v>158</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6456,20 +6518,18 @@
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6518,7 +6578,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6530,16 +6590,16 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6547,21 +6607,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>238</v>
+        <v>165</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6573,15 +6633,17 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6618,37 +6680,37 @@
         <v>77</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6659,44 +6721,46 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>240</v>
+        <v>171</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
       </c>
@@ -6720,49 +6784,49 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>163</v>
+        <v>77</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6773,10 +6837,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>242</v>
+        <v>182</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6799,18 +6863,20 @@
         <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -6834,13 +6900,13 @@
         <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>77</v>
@@ -6858,7 +6924,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6867,16 +6933,16 @@
         <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6887,10 +6953,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>249</v>
+        <v>194</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6898,7 +6964,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>86</v>
@@ -6916,27 +6982,29 @@
         <v>100</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>77</v>
@@ -6948,13 +7016,13 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>253</v>
+        <v>77</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>254</v>
+        <v>77</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -6972,7 +7040,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>255</v>
+        <v>201</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6987,13 +7055,13 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7001,10 +7069,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>257</v>
+        <v>206</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7012,7 +7080,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>86</v>
@@ -7027,16 +7095,16 @@
         <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7050,7 +7118,7 @@
         <v>77</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>77</v>
@@ -7086,7 +7154,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>261</v>
+        <v>211</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7101,13 +7169,13 @@
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>262</v>
+        <v>213</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7115,10 +7183,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7141,24 +7209,22 @@
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>288</v>
+        <v>77</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>77</v>
@@ -7200,7 +7266,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7215,13 +7281,13 @@
         <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>129</v>
+        <v>222</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7229,14 +7295,12 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7257,18 +7321,18 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>144</v>
+        <v>226</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7316,39 +7380,39 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>143</v>
+        <v>230</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>151</v>
+        <v>231</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>154</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7371,13 +7435,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7428,7 +7492,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7446,7 +7510,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7457,10 +7521,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>161</v>
+        <v>237</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7489,7 +7553,7 @@
         <v>133</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>135</v>
@@ -7530,10 +7594,10 @@
         <v>77</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>77</v>
@@ -7542,7 +7606,7 @@
         <v>149</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7560,7 +7624,7 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7571,10 +7635,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>166</v>
+        <v>239</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7591,26 +7655,24 @@
         <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>167</v>
+        <v>240</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>168</v>
+        <v>241</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7634,13 +7696,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7658,7 +7720,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7667,16 +7729,16 @@
         <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7687,10 +7749,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>176</v>
+        <v>246</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7713,20 +7775,18 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>178</v>
+        <v>247</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -7750,13 +7810,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -7774,7 +7834,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7789,10 +7849,10 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7803,10 +7863,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7814,7 +7874,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>86</v>
@@ -7829,32 +7889,30 @@
         <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>297</v>
+        <v>77</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>77</v>
@@ -7890,7 +7948,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>192</v>
+        <v>258</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7905,13 +7963,13 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>194</v>
+        <v>259</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -7919,10 +7977,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7930,7 +7988,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>86</v>
@@ -7945,16 +8003,16 @@
         <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7962,13 +8020,13 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>77</v>
+        <v>305</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>77</v>
@@ -8004,7 +8062,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>201</v>
+        <v>266</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8019,13 +8077,13 @@
         <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>203</v>
+        <v>129</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8033,12 +8091,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8059,16 +8119,18 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>206</v>
+        <v>144</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>207</v>
+        <v>145</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8116,39 +8178,39 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>210</v>
+        <v>151</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>212</v>
+        <v>153</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>77</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>213</v>
+        <v>158</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8168,20 +8230,18 @@
         <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8230,7 +8290,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8242,16 +8302,16 @@
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8259,21 +8319,21 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>238</v>
+        <v>165</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -8285,15 +8345,17 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8330,37 +8392,37 @@
         <v>77</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -8371,44 +8433,46 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>240</v>
+        <v>171</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
       </c>
@@ -8432,49 +8496,49 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>163</v>
+        <v>77</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8485,10 +8549,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>242</v>
+        <v>182</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8511,18 +8575,20 @@
         <v>87</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
       </c>
@@ -8546,13 +8612,13 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -8570,7 +8636,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8579,16 +8645,16 @@
         <v>86</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8599,10 +8665,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>249</v>
+        <v>194</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8610,7 +8676,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>86</v>
@@ -8628,27 +8694,29 @@
         <v>100</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>250</v>
+        <v>313</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>77</v>
@@ -8660,13 +8728,13 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>253</v>
+        <v>77</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>254</v>
+        <v>77</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -8684,7 +8752,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>255</v>
+        <v>201</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8699,13 +8767,13 @@
         <v>98</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -8713,10 +8781,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>257</v>
+        <v>206</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8724,7 +8792,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>86</v>
@@ -8739,16 +8807,16 @@
         <v>87</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>258</v>
+        <v>316</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8762,7 +8830,7 @@
         <v>77</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>77</v>
@@ -8798,7 +8866,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>261</v>
+        <v>211</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8813,13 +8881,13 @@
         <v>98</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>262</v>
+        <v>213</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -8827,10 +8895,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8853,24 +8921,22 @@
         <v>87</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>77</v>
@@ -8912,7 +8978,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8927,13 +8993,13 @@
         <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>129</v>
+        <v>222</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -8941,10 +9007,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>308</v>
+        <v>225</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8961,32 +9027,28 @@
         <v>77</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>309</v>
+        <v>226</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>310</v>
+        <v>227</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>311</v>
+        <v>228</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q65" t="s" s="2">
-        <v>314</v>
-      </c>
+      <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9030,7 +9092,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>308</v>
+        <v>230</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9045,16 +9107,16 @@
         <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>315</v>
+        <v>231</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>316</v>
+        <v>232</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>317</v>
+        <v>233</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>318</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66">
@@ -9062,7 +9124,7 @@
         <v>319</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>319</v>
+        <v>235</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9073,7 +9135,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
@@ -9082,23 +9144,19 @@
         <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9122,11 +9180,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z66" t="s" s="2">
-        <v>324</v>
+        <v>77</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -9144,50 +9204,50 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>319</v>
+        <v>162</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>325</v>
+        <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>326</v>
+        <v>163</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9196,23 +9256,21 @@
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>329</v>
+        <v>133</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>330</v>
+        <v>166</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
       </c>
@@ -9248,40 +9306,40 @@
         <v>77</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>328</v>
+        <v>169</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>333</v>
+        <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>334</v>
+        <v>163</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>335</v>
+        <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
@@ -9289,10 +9347,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>336</v>
+        <v>239</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9303,7 +9361,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -9312,23 +9370,21 @@
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>337</v>
+        <v>240</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>338</v>
+        <v>241</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9376,16 +9432,16 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>336</v>
+        <v>243</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>98</v>
@@ -9394,7 +9450,7 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>334</v>
+        <v>129</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9405,10 +9461,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>341</v>
+        <v>246</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9419,7 +9475,7 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>77</v>
@@ -9428,23 +9484,21 @@
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>342</v>
+        <v>100</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>343</v>
+        <v>247</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>344</v>
+        <v>248</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
@@ -9468,13 +9522,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9492,28 +9546,28 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>341</v>
+        <v>252</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>348</v>
+        <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>349</v>
+        <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>350</v>
+        <v>129</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>351</v>
+        <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -9521,10 +9575,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>352</v>
+        <v>323</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>352</v>
+        <v>254</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9535,7 +9589,7 @@
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
@@ -9544,23 +9598,21 @@
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>353</v>
+        <v>144</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>354</v>
+        <v>255</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>355</v>
+        <v>256</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
       </c>
@@ -9608,28 +9660,28 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>352</v>
+        <v>258</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>359</v>
+        <v>98</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>361</v>
+        <v>259</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>362</v>
+        <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
@@ -9637,10 +9689,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>363</v>
+        <v>324</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>363</v>
+        <v>261</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9663,24 +9715,24 @@
         <v>87</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>364</v>
+        <v>262</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>77</v>
+        <v>325</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>77</v>
@@ -9722,7 +9774,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>363</v>
+        <v>266</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9737,13 +9789,13 @@
         <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>315</v>
+        <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>367</v>
+        <v>129</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -9751,10 +9803,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>368</v>
+        <v>326</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>368</v>
+        <v>326</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9765,36 +9817,38 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>369</v>
+        <v>327</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>370</v>
+        <v>328</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>371</v>
+        <v>329</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>372</v>
+        <v>330</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q72" s="2"/>
+      <c r="Q72" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="R72" t="s" s="2">
         <v>77</v>
       </c>
@@ -9838,13 +9892,13 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>368</v>
+        <v>326</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>77</v>
@@ -9853,24 +9907,24 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>77</v>
+        <v>333</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>374</v>
+        <v>334</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>77</v>
+        <v>335</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>77</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9881,7 +9935,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>77</v>
@@ -9890,19 +9944,23 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>157</v>
+        <v>338</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
       </c>
@@ -9926,13 +9984,11 @@
         <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
@@ -9950,50 +10006,50 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>159</v>
+        <v>337</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>160</v>
+        <v>344</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>77</v>
+        <v>345</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>376</v>
+        <v>346</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>376</v>
+        <v>346</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
@@ -10002,21 +10058,23 @@
         <v>77</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>133</v>
+        <v>347</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>162</v>
+        <v>348</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
@@ -10064,28 +10122,28 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>165</v>
+        <v>346</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>77</v>
+        <v>351</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>160</v>
+        <v>352</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>77</v>
+        <v>353</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>77</v>
@@ -10093,14 +10151,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>378</v>
+        <v>77</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10113,25 +10171,25 @@
         <v>77</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>135</v>
+        <v>357</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>141</v>
+        <v>358</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -10180,7 +10238,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>381</v>
+        <v>354</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10192,13 +10250,13 @@
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>129</v>
+        <v>352</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -10209,10 +10267,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>382</v>
+        <v>359</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>382</v>
+        <v>359</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10223,7 +10281,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>77</v>
@@ -10235,17 +10293,19 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>177</v>
+        <v>360</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="O76" t="s" s="2">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10270,13 +10330,13 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>386</v>
+        <v>77</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>387</v>
+        <v>77</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -10294,28 +10354,28 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>382</v>
+        <v>359</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>77</v>
+        <v>365</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>98</v>
+        <v>366</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>77</v>
+        <v>367</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>77</v>
+        <v>369</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>77</v>
@@ -10323,10 +10383,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10337,7 +10397,7 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>77</v>
@@ -10349,17 +10409,19 @@
         <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="O77" t="s" s="2">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10408,28 +10470,28 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>376</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>98</v>
+        <v>377</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>77</v>
+        <v>380</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>77</v>
@@ -10437,10 +10499,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10451,7 +10513,7 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -10460,20 +10522,20 @@
         <v>77</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>342</v>
+        <v>226</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -10522,13 +10584,13 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
@@ -10537,13 +10599,13 @@
         <v>98</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>400</v>
+        <v>333</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>77</v>
@@ -10551,10 +10613,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10565,7 +10627,7 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -10577,19 +10639,19 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -10638,28 +10700,28 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>404</v>
+        <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>361</v>
+        <v>392</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>362</v>
+        <v>77</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>77</v>
@@ -10667,10 +10729,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10681,7 +10743,7 @@
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>77</v>
@@ -10693,18 +10755,16 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>406</v>
+        <v>159</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>407</v>
+        <v>160</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>408</v>
+        <v>161</v>
       </c>
       <c r="N80" s="2"/>
-      <c r="O80" t="s" s="2">
-        <v>409</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>77</v>
       </c>
@@ -10752,30 +10812,830 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z83" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AG80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH80" t="s" s="2">
+      <c r="AA83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
+      <c r="H85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AK80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN80" t="s" s="2">
+      <c r="AK85" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-ips-organization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-ips-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T11:57:38+00:00</t>
+    <t>2025-01-29T12:25:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
